--- a/data/trans_dic/P21B_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P21B_R-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,4%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>93,76; 100,0</t>
+          <t>93,49; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>94,1; 100,0</t>
+          <t>93,75; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>83,53; 95,7</t>
+          <t>84,05; 95,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>73,05; 100,0</t>
+          <t>69,58; 100,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>93,92; 99,35</t>
+          <t>94,1; 99,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,99; 99,27</t>
+          <t>94,07; 99,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,88; 97,11</t>
+          <t>85,85; 97,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>81,64; 98,08</t>
+          <t>85,1; 98,54</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>94,92; 99,18</t>
+          <t>95,11; 99,18</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>95,43; 99,19</t>
+          <t>95,33; 99,19</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>87,99; 95,86</t>
+          <t>87,03; 95,31</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>81,79; 97,33</t>
+          <t>83,26; 97,51</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>91,45%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>89,65; 97,75</t>
+          <t>89,76; 98,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>92,98; 98,75</t>
+          <t>92,89; 98,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>80,18; 94,37</t>
+          <t>80,25; 93,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>87,22; 100,0</t>
+          <t>90,68; 100,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>90,33; 97,36</t>
+          <t>90,49; 97,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>90,0; 96,71</t>
+          <t>89,88; 96,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>82,53; 93,57</t>
+          <t>81,99; 93,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>78,27; 91,94</t>
+          <t>78,94; 91,73</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>91,53; 97,01</t>
+          <t>91,56; 97,0</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>92,36; 96,99</t>
+          <t>92,43; 96,98</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>83,99; 92,57</t>
+          <t>83,72; 92,19</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>85,53; 94,74</t>
+          <t>86,48; 94,9</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,55%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>93,0; 100,0</t>
+          <t>93,25; 100,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>90,51; 99,28</t>
+          <t>90,24; 99,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>86,88; 97,51</t>
+          <t>86,04; 98,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>82,28; 94,45</t>
+          <t>82,0; 94,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>94,43; 99,39</t>
+          <t>94,11; 99,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>95,56; 99,48</t>
+          <t>95,59; 99,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>79,63; 92,21</t>
+          <t>79,69; 91,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>89,11; 96,47</t>
+          <t>89,45; 96,38</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>95,43; 99,55</t>
+          <t>95,63; 99,19</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>94,77; 99,06</t>
+          <t>94,79; 99,24</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>84,86; 93,36</t>
+          <t>85,38; 93,62</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>87,87; 94,66</t>
+          <t>87,94; 94,41</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,3%</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>83,97; 97,48</t>
+          <t>83,92; 97,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>89,35; 98,98</t>
+          <t>90,16; 98,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>85,3; 97,73</t>
+          <t>84,76; 97,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>85,47; 94,68</t>
+          <t>85,43; 94,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1162,37 +1162,37 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,45; 97,59</t>
+          <t>86,88; 97,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,32; 99,01</t>
+          <t>90,62; 98,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>84,21; 92,33</t>
+          <t>84,27; 92,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>93,34; 98,97</t>
+          <t>92,87; 98,94</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>89,93; 97,17</t>
+          <t>90,11; 97,3</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>90,05; 97,46</t>
+          <t>90,25; 97,39</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>86,38; 92,25</t>
+          <t>86,06; 92,11</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>91,07%</t>
         </is>
       </c>
     </row>
@@ -1277,52 +1277,52 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>78,51; 96,73</t>
+          <t>78,31; 96,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>90,13; 100,0</t>
+          <t>91,4; 100,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>89,12; 100,0</t>
+          <t>89,44; 100,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>85,81; 95,33</t>
+          <t>84,87; 95,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>87,49; 98,63</t>
+          <t>86,9; 98,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>94,99; 100,0</t>
+          <t>94,74; 100,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>87,89; 100,0</t>
+          <t>88,45; 100,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>86,49; 94,25</t>
+          <t>86,44; 94,4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>86,77; 96,62</t>
+          <t>87,33; 96,43</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>94,86; 99,45</t>
+          <t>94,76; 99,45</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>87,05; 93,52</t>
+          <t>87,94; 93,81</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>90,74%</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>91,2; 100,0</t>
+          <t>90,23; 100,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1427,52 +1427,52 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>89,54; 100,0</t>
+          <t>88,27; 100,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>76,7; 92,05</t>
+          <t>78,1; 92,64</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>92,55; 99,22</t>
+          <t>92,49; 99,22</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>93,64; 100,0</t>
+          <t>92,74; 100,0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>88,82; 98,71</t>
+          <t>88,7; 98,72</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>92,46; 99,69</t>
+          <t>89,51; 96,84</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>94,34; 98,93</t>
+          <t>93,98; 98,97</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>95,74; 100,0</t>
+          <t>95,45; 100,0</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>91,54; 98,53</t>
+          <t>91,73; 98,65</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>89,38; 99,13</t>
+          <t>86,75; 93,83</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,19%</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>85,97; 100,0</t>
+          <t>86,05; 100,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1567,52 +1567,52 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>77,97; 96,06</t>
+          <t>77,58; 96,24</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>86,84; 97,81</t>
+          <t>87,84; 97,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>89,85; 98,87</t>
+          <t>90,3; 98,86</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,32; 100,0</t>
+          <t>96,05; 100,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,53; 98,73</t>
+          <t>89,26; 98,72</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>92,87; 98,71</t>
+          <t>93,46; 98,55</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>91,48; 98,53</t>
+          <t>91,01; 98,25</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>97,62; 100,0</t>
+          <t>97,17; 100,0</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>89,22; 97,3</t>
+          <t>88,79; 97,13</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>93,21; 97,92</t>
+          <t>93,13; 97,99</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>91,53%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>93,33; 96,91</t>
+          <t>93,1; 96,98</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>95,88; 98,46</t>
+          <t>95,99; 98,57</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>90,09; 94,58</t>
+          <t>90,25; 94,67</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>88,66; 93,49</t>
+          <t>88,48; 93,29</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>95,29; 97,81</t>
+          <t>95,36; 97,81</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>95,58; 97,89</t>
+          <t>95,44; 97,91</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>90,33; 94,61</t>
+          <t>90,08; 94,52</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>90,89; 96,5</t>
+          <t>89,83; 93,19</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>95,04; 97,16</t>
+          <t>95,08; 97,2</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>96,08; 97,81</t>
+          <t>96,06; 97,84</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>91,07; 94,09</t>
+          <t>91,18; 94,18</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>90,95; 95,08</t>
+          <t>89,96; 92,83</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>69945</t>
+          <t>66795</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>75822</t>
+          <t>89080</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>145767</t>
+          <t>155875</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>92166; 98304</t>
+          <t>91908; 98304</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>102132; 108538</t>
+          <t>101749; 108538</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>77306; 88572</t>
+          <t>77788; 88774</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>55431; 75878</t>
+          <t>51252; 73657</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>104718; 110780</t>
+          <t>104920; 110767</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>120446; 127214</t>
+          <t>120550; 127207</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>79284; 89660</t>
+          <t>79264; 89710</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>66447; 79829</t>
+          <t>80878; 93654</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>199140; 208091</t>
+          <t>199547; 208091</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>225867; 234782</t>
+          <t>225628; 234778</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>162669; 177222</t>
+          <t>160886; 176201</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>128629; 153061</t>
+          <t>140454; 164493</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>86052</t>
+          <t>95742</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>105569</t>
+          <t>112758</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>191621</t>
+          <t>208502</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>99834; 108859</t>
+          <t>99956; 109437</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>151622; 161033</t>
+          <t>151467; 160728</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>75775; 89182</t>
+          <t>75836; 88660</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>76987; 88270</t>
+          <t>88384; 97465</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>167335; 180366</t>
+          <t>167630; 180867</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>191218; 205473</t>
+          <t>190961; 205684</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>115973; 131480</t>
+          <t>115219; 131020</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>96082; 112871</t>
+          <t>103027; 119725</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>271494; 287756</t>
+          <t>271583; 287708</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>346844; 364219</t>
+          <t>347102; 364183</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>197393; 217557</t>
+          <t>196752; 216671</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>180486; 199939</t>
+          <t>197168; 216359</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>105020</t>
+          <t>114834</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>122248</t>
+          <t>141128</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>227267</t>
+          <t>255961</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>82409; 88613</t>
+          <t>82635; 88613</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>112922; 123870</t>
+          <t>112589; 123822</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>91625; 102840</t>
+          <t>90741; 103467</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>96553; 110837</t>
+          <t>105460; 121102</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>129486; 136288</t>
+          <t>129050; 136277</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>160868; 167460</t>
+          <t>160908; 167439</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>113221; 131110</t>
+          <t>113310; 130238</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>116337; 125941</t>
+          <t>135045; 145510</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>215431; 224726</t>
+          <t>215870; 223911</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>277781; 290340</t>
+          <t>277819; 290889</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>210155; 231217</t>
+          <t>211462; 231846</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>217815; 234661</t>
+          <t>245865; 263940</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>142919</t>
+          <t>156000</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>144095</t>
+          <t>156498</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>287015</t>
+          <t>312498</t>
         </is>
       </c>
     </row>
@@ -2692,22 +2692,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>66465; 77163</t>
+          <t>66426; 77253</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>88340; 97861</t>
+          <t>89146; 97844</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>76097; 87177</t>
+          <t>75607; 87060</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>135197; 149755</t>
+          <t>148041; 163189</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2717,37 +2717,37 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>112262; 126719</t>
+          <t>112817; 126275</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>100698; 110386</t>
+          <t>101029; 110336</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>136454; 149613</t>
+          <t>148878; 162578</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>170883; 181195</t>
+          <t>170021; 181139</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>205693; 222254</t>
+          <t>206098; 222541</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>180736; 195592</t>
+          <t>181121; 195453</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>276621; 295406</t>
+          <t>301162; 322331</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>104175</t>
+          <t>113470</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>118932</t>
+          <t>133346</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>223107</t>
+          <t>246816</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>49547; 61041</t>
+          <t>49420; 61026</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>67181; 74542</t>
+          <t>68129; 74542</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>60678; 68086</t>
+          <t>60899; 68086</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>98309; 109219</t>
+          <t>105439; 118255</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>75620; 85246</t>
+          <t>75112; 85256</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>98911; 104128</t>
+          <t>98652; 104128</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>78083; 88841</t>
+          <t>78579; 88841</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>113217; 123366</t>
+          <t>126870; 138554</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>129748; 144490</t>
+          <t>130584; 144199</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>169479; 177682</t>
+          <t>169314; 177686</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>143584; 155712</t>
+          <t>143590; 155726</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>213675; 229547</t>
+          <t>238316; 254239</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>55214</t>
+          <t>62211</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>290885</t>
+          <t>95690</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>346100</t>
+          <t>157900</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>55887; 61279</t>
+          <t>55293; 61279</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -3118,52 +3118,52 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>51002; 56961</t>
+          <t>50277; 56961</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>49122; 58952</t>
+          <t>56140; 66590</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>87596; 93916</t>
+          <t>87546; 93916</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>86266; 92124</t>
+          <t>85432; 92124</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>68367; 75979</t>
+          <t>68278; 75991</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>274173; 295621</t>
+          <t>91416; 98901</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>147103; 154268</t>
+          <t>146544; 154325</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>142283; 148621</t>
+          <t>141854; 148621</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>122602; 131963</t>
+          <t>122860; 132123</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>322266; 357450</t>
+          <t>150951; 163279</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>54587</t>
+          <t>59886</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>118574</t>
+          <t>128603</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>173161</t>
+          <t>188487</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>48683; 56629</t>
+          <t>48732; 56629</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3326,52 +3326,52 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>34852; 42938</t>
+          <t>34677; 43016</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>50318; 56670</t>
+          <t>55622; 62036</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>94462; 103938</t>
+          <t>94932; 103928</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>137058; 142291</t>
+          <t>136669; 142291</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>86810; 95736</t>
+          <t>86553; 95724</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>113592; 120736</t>
+          <t>123955; 130705</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>147974; 159376</t>
+          <t>147220; 158934</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>214392; 219614</t>
+          <t>213408; 219614</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>126391; 137832</t>
+          <t>125787; 137589</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>168010; 176509</t>
+          <t>182493; 192013</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>617913</t>
+          <t>668936</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>976126</t>
+          <t>857103</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1594039</t>
+          <t>1526040</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>521171; 541164</t>
+          <t>519926; 541582</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>674598; 692771</t>
+          <t>675363; 693539</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>496819; 521563</t>
+          <t>497676; 522076</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>599556; 632172</t>
+          <t>648060; 683339</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>785172; 805944</t>
+          <t>785811; 805989</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>934131; 956720</t>
+          <t>932772; 956899</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>676864; 708890</t>
+          <t>674988; 708250</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>951186; 1009867</t>
+          <t>839627; 871099</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1313868; 1343182</t>
+          <t>1314420; 1343697</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1615024; 1644064</t>
+          <t>1614688; 1644620</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1184632; 1223872</t>
+          <t>1186026; 1225070</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1566789; 1637961</t>
+          <t>1499867; 1547622</t>
         </is>
       </c>
     </row>
